--- a/Result/profitability/2373.xlsx
+++ b/Result/profitability/2373.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8937499999999999</v>
+        <v>0.8462499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>43.76</v>
+        <v>43.55249999999999</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.49</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7925</v>
+        <v>0.775</v>
       </c>
       <c r="N3" t="n">
-        <v>42.55625</v>
+        <v>43.2075</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.49</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7212500000000001</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>42.4925</v>
+        <v>42.4225</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>0.64</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7125</v>
+        <v>0.69375</v>
       </c>
       <c r="N5" t="n">
-        <v>41.36375</v>
+        <v>41.13</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.38</v>
       </c>
       <c r="M6" t="n">
-        <v>0.62625</v>
+        <v>0.61625</v>
       </c>
       <c r="N6" t="n">
-        <v>40.14250000000001</v>
+        <v>40.0275</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0.545</v>
+        <v>0.52375</v>
       </c>
       <c r="N7" t="n">
-        <v>39.1725</v>
+        <v>39.4875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.61</v>
       </c>
       <c r="M8" t="n">
-        <v>0.485</v>
+        <v>0.51</v>
       </c>
       <c r="N8" t="n">
-        <v>38.5775</v>
+        <v>38.5875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.48875</v>
       </c>
       <c r="N9" t="n">
-        <v>37.67375000000001</v>
+        <v>37.67375</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.56625</v>
       </c>
       <c r="N13" t="n">
-        <v>38.11499999999999</v>
+        <v>38.115</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2373</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2634</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1443</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1191</v>
+      </c>
+      <c r="F75" t="n">
+        <v>45.21</v>
+      </c>
+      <c r="G75" t="n">
+        <v>150</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.70%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>92</v>
+      </c>
+      <c r="J75" t="n">
+        <v>242</v>
+      </c>
+      <c r="K75" t="n">
+        <v>206</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.98375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>44.86</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2777777777777779</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.07999999999999829</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.001772656769333025</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1401869158878505</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.869999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.03971962616822422</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
